--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rd6771b63751c45bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rfee77356f65e45d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -455,7 +455,7 @@
         <x:v>任务ID</x:v>
       </x:c>
       <x:c r="B2" s="29" t="str">
-        <x:v>ale-q2827</x:v>
+        <x:v>developer_sandbox_resource_precheck</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -463,15 +463,15 @@
         <x:v>主软件</x:v>
       </x:c>
       <x:c r="B3" s="30" t="str">
-        <x:v>kubectl1.32.6</x:v>
+        <x:v>Kubernetes</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="37" t="str">
-        <x:v>业务目标</x:v>
+        <x:v>辅助工具</x:v>
       </x:c>
       <x:c r="B4" s="30" t="str">
-        <x:v>开发者沙箱LimitRange与ResourceQuota预检表</x:v>
+        <x:v>kubectl1.32.6、PowerShell7、Ruby3.3、CSV查看器和JSON查看器</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -479,131 +479,144 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="30" t="str">
-        <x:v>题目输入数据包中的虚构或脱敏材料</x:v>
+        <x:v>沙箱平台组提供的Pod与PVC申请、现有用量、资源规则和故障处理约定</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="37" t="str">
-        <x:v>输入边界</x:v>
+        <x:v>输入获取方式</x:v>
       </x:c>
       <x:c r="B6" s="30" t="str">
-        <x:v>输入目录只读，生成内容写入独立工作目录</x:v>
+        <x:v>从平台组交接目录取得输入数据包并解压到Windows11本地目录</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="37" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B7" s="30" t="str">
-        <x:v>修正Namespace、LimitRange和ResourceQuota→用kubectl客户端模式生成并核对对象→逐容器补齐四个资源字段并保留来源→检查min、max和limit与request比值→根据现有用量计算七项配额增量→把结论记录为提交前预检而非准入结果</x:v>
+        <x:v>broken_policy.yaml、existing_usage.json、fault_policy.json、precheck_contract.json、requests目录和README.md</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="37" t="str">
-        <x:v>交付路径</x:v>
+        <x:v>目标输出文件</x:v>
       </x:c>
       <x:c r="B8" s="30" t="str">
-        <x:v>output/policy/00-namespace.yaml；output/policy/10-limitrange.yaml；output/policy/20-resourcequota.yaml；output/run_precheck.rb；output/results/request_precheck.csv；output/results/normalized_containers.csv；output/results/quota_trajectory.csv；output/results/precheck_summary.json；output/results/validation.json</x:v>
+        <x:v>output/policy、output/results和output/README.md下的完整交付物</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A9" s="37" t="str">
-        <x:v>固定字段</x:v>
+        <x:v>核心操作链</x:v>
       </x:c>
       <x:c r="B9" s="30" t="str">
-        <x:v>precheck_contract.json的contract_id为internet-sandbox-precheck-v3；request_precheck.csv的decision为WITHIN_POLICY或NEEDS_CHANGE；precheck_summary.json的api_server_contacted为false；precheck_summary.json的workloads_created为false</x:v>
+        <x:v>修正资源对象→核对客户端对象→补齐容器资源字段→检查LimitRange边界→累计ResourceQuota用量→整理预检结果</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A10" s="37" t="str">
-        <x:v>固定集合</x:v>
+        <x:v>资源对象</x:v>
       </x:c>
       <x:c r="B10" s="30" t="str">
-        <x:v>Kubernetes对象包含Namespace；LimitRange；ResourceQuota；预检原因包含LIMIT_RANGE；RESOURCE_QUOTA；结果文件包含final_usage.json；kubectl_namespace_dry_run.yaml；kubectl_quota_dry_run.yaml；normalized_containers.csv；precheck_summary.json；quota_trajectory.csv；request_precheck.csv；validation.json</x:v>
+        <x:v>Namespace名称为internet-sandbox；LimitRange包含defaultRequest、default、min、max和limit与request比值；ResourceQuota包含合同声明的七项资源</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="37" t="str">
-        <x:v>固定数值</x:v>
+        <x:v>默认值补齐</x:v>
       </x:c>
       <x:c r="B11" s="30" t="str">
-        <x:v>申请输入的申请数为10份；容器归一表的数据行为9行；累计用量轨迹的数据行为11行；离线预检的WITHIN_POLICY数量为5份；离线预检的NEEDS_CHANGE数量为5份</x:v>
+        <x:v>保留申请中已有的CPU与内存值，只对缺失字段使用precheck_contract.json中的默认值，并逐字段记录来源</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>允许变体</x:v>
+        <x:v>LimitRange边界</x:v>
       </x:c>
       <x:c r="B12" s="30" t="str">
-        <x:v>允许Kubernetes等价单位表示</x:v>
+        <x:v>在容器资源字段完整后检查CPU与内存的min、max和limit与request比值，原因使用合同定义的资源枚举</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Windows复现</x:v>
+        <x:v>ResourceQuota累计</x:v>
       </x:c>
       <x:c r="B13" s="30" t="str">
-        <x:v>主软件为kubectl1.32.6，使用Windows11原生PowerShell运行kubectl.exe。复现过程只执行客户端版本查询和dry-run生成命令，不读取用户kubeconfig、不连接集群，也不创建Kubernetes对象。
-辅助工具为Ruby3.3及其标准库。kubectl与Kubernetes按ApacheLicense2.0使用，Ruby沿用原项目许可。
-安装锁定工具时可以联网；正式复现只读取输入包和本地工作目录，不访问API服务器或外部服务。读写权限限定为输入目录只读、结果目录可写。
-主要风险是漏补同一resources映射中的单个字段、按quantity字符串外观误判等值、把超出规则的申请计入累计用量，或把离线预检写成API服务器准入结果。</x:v>
+        <x:v>从existing_usage.json开始按申请顺序累计七项资源；LimitRange未通过或累计后超过hard的申请不进入后续用量</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A14" s="37" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>预检结论</x:v>
       </x:c>
       <x:c r="B14" s="30" t="str">
-        <x:v>总分100分。；1.三份Kubernetes对象的身份和资源规则正确（20分）；2.逐字段默认值及来源记录正确（20分）；3.LimitRange规则检查正确（20分）；4.ResourceQuota增量和累计用量计算正确（25分）；5.结果没有API服务器准入或拒绝的运行期结论（15分）</x:v>
+        <x:v>每个request_id对应一条WITHIN_POLICY或NEEDS_CHANGE结论，明细、轨迹、最终用量与摘要相互一致</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="37" t="str">
+        <x:v>客户端对象</x:v>
+      </x:c>
+      <x:c r="B15" s="30" t="str">
+        <x:v>kubectl客户端模式生成Namespace与ResourceQuota对象，现场提交和集群侧核查由平台值班继续处理</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A16" s="37" t="str">
+        <x:v>现场接续</x:v>
+      </x:c>
+      <x:c r="B16" s="30" t="str">
+        <x:v>平台值班根据预检表调整申请，提交前按最新用量复核配额，再执行维护窗内的集群操作</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="37" t="str">
+        <x:v>完成条件</x:v>
+      </x:c>
+      <x:c r="B17" s="30" t="str">
+        <x:v>三份Kubernetes对象可解析，申请预检表、容器字段表、配额轨迹、最终用量和摘要能够相互复算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A18" s="37" t="str">
+        <x:v>可验证点</x:v>
+      </x:c>
+      <x:c r="B18" s="30" t="str">
+        <x:v>对象身份、LimitRange默认值与边界、ResourceQuota资源集合、申请主键、字段来源、累计用量和预检结论</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="37" t="str">
         <x:v>不适合作为评分点的内容</x:v>
       </x:c>
-      <x:c r="B15" s="30" t="str">
-        <x:v>文件缩进、换行、等价代码组织和本地绝对路径</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A16" s="37" t="str"/>
-      <x:c r="B16" s="30" t="str"/>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="37" t="str"/>
-      <x:c r="B17" s="30" t="str"/>
-    </x:row>
-    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A18" s="37" t="str"/>
-      <x:c r="B18" s="30" t="str"/>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="37" t="str"/>
-      <x:c r="B19" s="30" t="str"/>
+      <x:c r="B19" s="30" t="str">
+        <x:v>YAML键序、CSV行序、JSON缩进、临时目录和说明文字风格</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A20" s="37" t="str"/>
-      <x:c r="B20" s="30" t="str"/>
+      <x:c r="A20" s="37"/>
+      <x:c r="B20" s="30"/>
     </x:row>
     <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A21" s="37" t="str"/>
-      <x:c r="B21" s="30" t="str"/>
+      <x:c r="A21" s="37"/>
+      <x:c r="B21" s="30"/>
     </x:row>
     <x:row r="22" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A22" s="37" t="str"/>
-      <x:c r="B22" s="30" t="str"/>
+      <x:c r="A22" s="37"/>
+      <x:c r="B22" s="30"/>
     </x:row>
     <x:row r="23" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A23" s="37" t="str"/>
-      <x:c r="B23" s="30" t="str"/>
+      <x:c r="A23" s="37"/>
+      <x:c r="B23" s="30"/>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="37" t="str"/>
-      <x:c r="B24" s="30" t="str"/>
+      <x:c r="A24" s="37"/>
+      <x:c r="B24" s="30"/>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A25" s="38" t="str"/>
-      <x:c r="B25" s="30" t="str"/>
+      <x:c r="A25" s="38"/>
+      <x:c r="B25" s="30"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
